--- a/content/srednie-veka-6/content.xlsx
+++ b/content/srednie-veka-6/content.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Легенда" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Даты" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Термины" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Персоналии" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Причины" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правда-ложь" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Уроки" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Главы" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параграфы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Даты" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Термины" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Персоналии" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Причины" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правда-ложь" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Уроки" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Главы" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,11 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,12 +75,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -460,110 +467,192 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Даты</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Одна строка — одна дата. assoc — ассоциация для запоминания (показывается при ошибке), more — мини-факт за значком «хочу все знать», hook — шутка при верном ответе</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Параграфы</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Список параграфов и их частей. Длинный параграф можно разрезать: две строки с id вида 21-22a / 21-22b, тот же id ставить фактам на других листах</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Термины</t>
+          <t>Даты</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Термин и определение. Дистракторы берутся из определений других терминов</t>
+          <t>Одна строка — одна дата. assoc — ассоциация для запоминания (показывается при ошибке), more — мини-факт за значком «хочу все знать», hook — шутка при верном ответе</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Персоналии</t>
+          <t>Термины</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Имя и кто это</t>
+          <t>Термин и определение. Дистракторы берутся из определений других терминов</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Причины</t>
+          <t>Персоналии</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Причина → верное следствие и два неверных</t>
+          <t>Имя и кто это</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Тексты</t>
+          <t>Причины</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Текст с пропусками {0} {1} {2}; ответы и лишние варианты через |</t>
+          <t>Причина → верное следствие и два неверных</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Правда-ложь</t>
+          <t>Тексты</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Утверждение, верно ли, пояснение для ложных</t>
+          <t>Текст с пропусками {0} {1} {2}; ответы и лишние варианты через |</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Уроки</t>
+          <t>Правда-ложь</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Разбивка дат по урокам (id через запятую). Урок = 8 заданий</t>
+          <t>Утверждение, верно ли, пояснение для ложных</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Главы</t>
+          <t>Уроки</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Какие параграфы в какой главе — для режима «Контрольная»</t>
+          <t>Разбивка дат по урокам (id через запятую). Урок = 8 заданий</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Главы</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Какие параграфы в какой главе — для режима «Контрольная»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Правило</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Правь любой лист, потом python3 tools/xlsx2json.py — и JSON обновится. Столбец id не менять</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Страны и народы Азии, Африки и Америки</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>15,16-17,18,19,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Осень Средневековья</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>21-22a,21-22b,23,24</t>
         </is>
       </c>
     </row>
@@ -573,6 +662,297 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>§15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Кочевники Великой степи и их соседи в Средние века</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Контрольная</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16-17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>§16-17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Китай и Япония в Средние века</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Контрольная</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>§18</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Индия в Средние века</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Контрольная</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>§19</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Народы и государства Африки</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Контрольная</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>§20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Цивилизации доколумбовой Америки</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Контрольная</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>21-22a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>§21-22 ·1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Столетняя война и Черная смерть</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>До конца учебника</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>21-22b</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>§21-22 ·2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Восстания, гуситы и конец войны</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>До конца учебника</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>§23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Гибель Византии и возникновение Османской империи</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>До конца учебника</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>§24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Европа на пороге Нового времени</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>До конца учебника</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2267,7 +2647,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2324,7 +2704,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2373,7 +2753,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2434,7 +2814,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2487,7 +2867,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2544,7 +2924,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2597,7 +2977,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2654,7 +3034,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2707,7 +3087,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2756,7 +3136,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2809,7 +3189,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2862,7 +3242,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2915,7 +3295,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2968,7 +3348,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3021,7 +3401,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3078,7 +3458,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3135,7 +3515,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3188,7 +3568,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3241,7 +3621,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3290,7 +3670,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3343,7 +3723,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3396,7 +3776,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4284,7 +4664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4827,7 +5207,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4847,7 +5227,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4867,7 +5247,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4887,7 +5267,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4907,7 +5287,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4927,7 +5307,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4947,7 +5327,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4967,7 +5347,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5186,7 +5566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5529,7 +5909,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5549,7 +5929,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5569,7 +5949,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5589,7 +5969,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5609,7 +5989,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -5629,7 +6009,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5649,7 +6029,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5669,7 +6049,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -5689,7 +6069,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -5709,7 +6089,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5729,7 +6109,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5928,7 +6308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6223,7 +6603,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6253,7 +6633,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6283,7 +6663,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6313,7 +6693,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6492,7 +6872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6741,7 +7121,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6766,7 +7146,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6791,7 +7171,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6915,7 +7295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7290,7 +7670,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7315,7 +7695,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7340,7 +7720,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7361,7 +7741,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7382,7 +7762,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7565,7 +7945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7748,7 +8128,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7768,7 +8148,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22a</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7788,7 +8168,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>21-22b</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7859,76 +8239,6 @@
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>86,87,90,91,92</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Страны и народы Азии, Африки и Америки</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>15,16-17,18,19,20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Осень Средневековья</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>21-22,23,24</t>
         </is>
       </c>
     </row>
